--- a/guide.xlsx
+++ b/guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEEA408-6B9F-42DA-B5A0-CC38826521B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5003E7CE-AAB4-4EF5-AE4E-D7E443B437A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18615" yWindow="0" windowWidth="10185" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guides" sheetId="1" r:id="rId1"/>
@@ -29,56 +29,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
-  <si>
-    <t>Автор</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>1.jpg</t>
-  </si>
-  <si>
-    <t>Описание</t>
-  </si>
-  <si>
-    <t>Название</t>
-  </si>
-  <si>
     <t>Раздел 1</t>
   </si>
   <si>
-    <t>Название справочника</t>
-  </si>
-  <si>
-    <t>изображение</t>
-  </si>
-  <si>
-    <t>автор</t>
-  </si>
-  <si>
-    <t>дата добавления</t>
-  </si>
-  <si>
-    <t>id справочника</t>
-  </si>
-  <si>
-    <t>название раздела</t>
-  </si>
-  <si>
-    <t>текст раздела</t>
-  </si>
-  <si>
-    <t>изображения</t>
-  </si>
-  <si>
-    <t>файлы</t>
-  </si>
-  <si>
-    <t>видео</t>
-  </si>
-  <si>
     <t>1.jpg, 2.jpg</t>
   </si>
   <si>
@@ -92,6 +50,51 @@
   </si>
   <si>
     <t xml:space="preserve">текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела </t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Иванов И.И.</t>
+  </si>
+  <si>
+    <t>img/html.jpg</t>
+  </si>
+  <si>
+    <t>HTML основы</t>
+  </si>
+  <si>
+    <t>CSS руководство</t>
+  </si>
+  <si>
+    <t>img/css.jpg</t>
+  </si>
+  <si>
+    <t>Петров П.П.</t>
+  </si>
+  <si>
+    <t>guide_id</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>images</t>
+  </si>
+  <si>
+    <t>files</t>
+  </si>
+  <si>
+    <t>videos</t>
   </si>
 </sst>
 </file>
@@ -127,8 +130,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -409,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -421,19 +425,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -441,20 +445,38 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45342</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -473,25 +495,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -502,19 +524,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -525,19 +547,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
